--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="136">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -244,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>Microbiology6305.OrderedTest</t>
+    <t>Microbiology6305.orderedTest</t>
   </si>
   <si>
     <t>1</t>
@@ -254,181 +257,181 @@
 </t>
   </si>
   <si>
-    <t>ORDERED TEST (.35)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.DatetimeSpecimenTaken</t>
+    <t>ORDERED TEST (-.35)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.datetimeSpecimenTaken</t>
   </si>
   <si>
     <t xml:space="preserve">Element
 </t>
   </si>
   <si>
-    <t>DATE/TIME SPECIMEN TAKEN (.01)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.DateReportCompleted</t>
-  </si>
-  <si>
-    <t>DATE REPORT COMPLETED (.03)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.VerifyPerson</t>
-  </si>
-  <si>
-    <t>VERIFY PERSON (.04)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.AccessioningInstitution</t>
-  </si>
-  <si>
-    <t>ACCESSIONING INSTITUTION (.112)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.CommentOnSpecimen</t>
-  </si>
-  <si>
-    <t>COMMENT ON SPECIMEN (.99)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.Organism</t>
+    <t>DATE/TIME SPECIMEN TAKEN (-.01)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.dateReportCompleted</t>
+  </si>
+  <si>
+    <t>DATE REPORT COMPLETED (-.03)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.verifyPerson</t>
+  </si>
+  <si>
+    <t>VERIFY PERSON (-.04)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.accessioningInstitution</t>
+  </si>
+  <si>
+    <t>ACCESSIONING INSTITUTION (-.112)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.commentOnSpecimen</t>
+  </si>
+  <si>
+    <t>COMMENT ON SPECIMEN (-.99)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.organism</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organism633)
 </t>
   </si>
   <si>
-    <t>ORGANISM (12)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.MicrobiologyAccession</t>
-  </si>
-  <si>
-    <t>MICROBIOLOGY ACCESSION (.06)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.Ien</t>
-  </si>
-  <si>
-    <t>IEN (.001)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.CollectionSample</t>
+    <t>ORGANISM (-12)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.microbiologyAccession</t>
+  </si>
+  <si>
+    <t>MICROBIOLOGY ACCESSION (-.06)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.ien</t>
+  </si>
+  <si>
+    <t>IEN (-.001)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.collectionSample</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/CollectionSample62)
 </t>
   </si>
   <si>
-    <t>COLLECTION SAMPLE (.055)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.BactRptRemark</t>
+    <t>COLLECTION SAMPLE (-.055)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.bactRptRemark</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/BactRptRemark6333)
 </t>
   </si>
   <si>
-    <t>BACT RPT REMARK (13)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.BactRptStatus</t>
-  </si>
-  <si>
-    <t>BACT RPT STATUS (11.5)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.UrineScreen</t>
-  </si>
-  <si>
-    <t>URINE SCREEN (11.57)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.SputumScreen</t>
-  </si>
-  <si>
-    <t>SPUTUM SCREEN (11.58)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.GramStain</t>
+    <t>BACT RPT REMARK (-13)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.bactRptStatus</t>
+  </si>
+  <si>
+    <t>BACT RPT STATUS (-11.5)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.urineScreen</t>
+  </si>
+  <si>
+    <t>URINE SCREEN (-11.57)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.sputumScreen</t>
+  </si>
+  <si>
+    <t>SPUTUM SCREEN (-11.58)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.gramStain</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/GramStain6329)
 </t>
   </si>
   <si>
-    <t>GRAM STAIN (11.6)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.ParasiteRptRemark</t>
+    <t>GRAM STAIN (-11.6)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasiteRptRemark</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
 </t>
   </si>
   <si>
-    <t>PARASITE RPT REMARK (17)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.ParasiteRptStatus</t>
-  </si>
-  <si>
-    <t>PARASITE RPT STATUS (15)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.MycologyRptRemark</t>
+    <t>PARASITE RPT REMARK (-17)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasiteRptStatus</t>
+  </si>
+  <si>
+    <t>PARASITE RPT STATUS (-15)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycologyRptRemark</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/MycologyRptRemark6338)
 </t>
   </si>
   <si>
-    <t>MYCOLOGY RPT REMARK (21)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.MycologyRptStatus</t>
-  </si>
-  <si>
-    <t>MYCOLOGY RPT STATUS (19)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.TbRptRemark</t>
+    <t>MYCOLOGY RPT REMARK (-21)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycologyRptStatus</t>
+  </si>
+  <si>
+    <t>MYCOLOGY RPT STATUS (-19)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.tbRptRemark</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/TbRptRemark6341)
 </t>
   </si>
   <si>
-    <t>TB RPT REMARK (27)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.TbRptStatus</t>
-  </si>
-  <si>
-    <t>TB RPT STATUS (23)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.AcidFastStain</t>
-  </si>
-  <si>
-    <t>ACID FAST STAIN (24)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.VirologyRptRemark</t>
+    <t>TB RPT REMARK (-27)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.tbRptStatus</t>
+  </si>
+  <si>
+    <t>TB RPT STATUS (-23)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.acidFastStain</t>
+  </si>
+  <si>
+    <t>ACID FAST STAIN (-24)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.virologyRptRemark</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VirologyRptRemark6344)
 </t>
   </si>
   <si>
-    <t>VIROLOGY RPT REMARK (37)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.VirologyReportStatus</t>
-  </si>
-  <si>
-    <t>VIROLOGY REPORT STATUS (34)</t>
+    <t>VIROLOGY RPT REMARK (-37)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.virologyReportStatus</t>
+  </si>
+  <si>
+    <t>VIROLOGY REPORT STATUS (-34)</t>
   </si>
 </sst>
 </file>
@@ -659,39 +662,41 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>3</v>
@@ -699,26 +704,26 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -731,8 +736,8 @@
   <dimension ref="A1:AJ26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.109375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.859375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -762,7 +767,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -770,112 +775,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2">
@@ -887,2493 +892,2495 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
       </c>
-      <c r="M2" s="2"/>
+      <c r="M2" t="s" s="2">
+        <v>22</v>
+      </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="139">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -257,7 +257,7 @@
 </t>
   </si>
   <si>
-    <t>ORDERED TEST (-.35)</t>
+    <t>ORDERED TEST (-.35) w/ binding http://va.gov/fhir/ValueSet/VSVFDiagnosticReportLabStatus-vista</t>
   </si>
   <si>
     <t>Microbiology6305.datetimeSpecimenTaken</t>
@@ -339,7 +339,17 @@
     <t>Microbiology6305.bactRptStatus</t>
   </si>
   <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
     <t>BACT RPT STATUS (-11.5)</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus-vista</t>
   </si>
   <si>
     <t>Microbiology6305.urineScreen</t>
@@ -761,7 +771,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.02734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -2111,13 +2121,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2144,13 +2154,11 @@
         <v>72</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>72</v>
@@ -2185,10 +2193,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2214,10 +2222,10 @@
         <v>82</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2268,7 +2276,7 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>73</v>
@@ -2285,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2314,10 +2322,10 @@
         <v>82</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2368,7 +2376,7 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
@@ -2385,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2411,13 +2419,13 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2468,7 +2476,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2485,10 +2493,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2511,13 +2519,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2568,7 +2576,7 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
@@ -2585,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2611,13 +2619,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2644,13 +2652,11 @@
         <v>72</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>72</v>
@@ -2668,7 +2674,7 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
@@ -2685,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2711,13 +2717,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2768,7 +2774,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -2785,10 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2811,13 +2817,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2844,13 +2850,11 @@
         <v>72</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>72</v>
@@ -2868,7 +2872,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -2885,10 +2889,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2911,13 +2915,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2968,7 +2972,7 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -2985,10 +2989,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3011,13 +3015,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3044,13 +3048,11 @@
         <v>72</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>72</v>
@@ -3068,7 +3070,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3085,10 +3087,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3114,10 +3116,10 @@
         <v>82</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3168,7 +3170,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3185,10 +3187,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3211,13 +3213,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3268,7 +3270,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3285,10 +3287,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3311,13 +3313,13 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3344,13 +3346,11 @@
         <v>72</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>72</v>
@@ -3368,7 +3368,7 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -257,7 +257,7 @@
 </t>
   </si>
   <si>
-    <t>ORDERED TEST (-.35) w/ binding http://va.gov/fhir/ValueSet/VSVFDiagnosticReportLabStatus-vista</t>
+    <t>ORDERED TEST (-.35)</t>
   </si>
   <si>
     <t>Microbiology6305.datetimeSpecimenTaken</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>-</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file MICROBIOLOGY (63.05)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -346,7 +346,7 @@
     <t>BACT RPT STATUS (-11.5)</t>
   </si>
   <si>
-    <t>example</t>
+    <t>preferred</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus-vista</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="137">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -336,58 +336,52 @@
     <t>BACT RPT REMARK (-13)</t>
   </si>
   <si>
-    <t>Microbiology6305.bactRptStatus</t>
+    <t>Microbiology6305.urineScreen</t>
+  </si>
+  <si>
+    <t>URINE SCREEN (-11.57)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.sputumScreen</t>
+  </si>
+  <si>
+    <t>SPUTUM SCREEN (-11.58)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.gramStain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/GramStain6329)
+</t>
+  </si>
+  <si>
+    <t>GRAM STAIN (-11.6)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasiteRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
+</t>
+  </si>
+  <si>
+    <t>PARASITE RPT REMARK (-17)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasiteRptStatus</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
 </t>
   </si>
   <si>
-    <t>BACT RPT STATUS (-11.5)</t>
+    <t>PARASITE RPT STATUS (-15)</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus-vista</t>
-  </si>
-  <si>
-    <t>Microbiology6305.urineScreen</t>
-  </si>
-  <si>
-    <t>URINE SCREEN (-11.57)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.sputumScreen</t>
-  </si>
-  <si>
-    <t>SPUTUM SCREEN (-11.58)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.gramStain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/GramStain6329)
-</t>
-  </si>
-  <si>
-    <t>GRAM STAIN (-11.6)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
-</t>
-  </si>
-  <si>
-    <t>PARASITE RPT REMARK (-17)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptStatus</t>
-  </si>
-  <si>
-    <t>PARASITE RPT STATUS (-15)</t>
   </si>
   <si>
     <t>Microbiology6305.mycologyRptRemark</t>
@@ -743,7 +737,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ26"/>
+  <dimension ref="A1:AJ25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.859375" customWidth="true" bestFit="true"/>
@@ -2121,13 +2115,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>107</v>
-      </c>
       <c r="M14" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2154,11 +2148,13 @@
         <v>72</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>72</v>
@@ -2193,10 +2189,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2222,10 +2218,10 @@
         <v>82</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2276,7 +2272,7 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>73</v>
@@ -2293,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2319,13 +2315,13 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2376,7 +2372,7 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
@@ -2393,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2419,13 +2415,13 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2476,7 +2472,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2493,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2519,13 +2515,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2552,13 +2548,11 @@
         <v>72</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>72</v>
@@ -2576,7 +2570,7 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
@@ -2619,13 +2613,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2652,11 +2646,13 @@
         <v>72</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>72</v>
@@ -2691,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2717,7 +2713,7 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>124</v>
@@ -2750,13 +2746,11 @@
         <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>72</v>
@@ -2774,7 +2768,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -2817,13 +2811,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2850,11 +2844,13 @@
         <v>72</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>72</v>
@@ -2889,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2915,7 +2911,7 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>129</v>
@@ -2948,13 +2944,11 @@
         <v>72</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>72</v>
@@ -2972,7 +2966,7 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -3015,7 +3009,7 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>131</v>
@@ -3048,11 +3042,13 @@
         <v>72</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>72</v>
@@ -3113,13 +3109,13 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3187,10 +3183,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3213,7 +3209,7 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>136</v>
@@ -3246,13 +3242,11 @@
         <v>72</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>72</v>
@@ -3270,7 +3264,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3282,104 +3276,6 @@
         <v>72</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K26" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q26" s="2"/>
-      <c r="R26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y26" s="2"/>
-      <c r="Z26" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="108">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,10 +247,38 @@
     <t>Base</t>
   </si>
   <si>
+    <t>Microbiology6305.datetimeSpecimenTaken</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Element
+</t>
+  </si>
+  <si>
+    <t>DATE/TIME SPECIMEN TAKEN (-.01)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.commentOnSpecimen</t>
+  </si>
+  <si>
+    <t>COMMENT ON SPECIMEN (-.99)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.microbiologyAccession</t>
+  </si>
+  <si>
+    <t>MICROBIOLOGY ACCESSION (-.06)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.ien</t>
+  </si>
+  <si>
+    <t>IEN (-.001)</t>
+  </si>
+  <si>
     <t>Microbiology6305.orderedTest</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/OrderedTest635)
@@ -260,60 +288,10 @@
     <t>ORDERED TEST (-.35)</t>
   </si>
   <si>
-    <t>Microbiology6305.datetimeSpecimenTaken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Element
-</t>
-  </si>
-  <si>
-    <t>DATE/TIME SPECIMEN TAKEN (-.01)</t>
-  </si>
-  <si>
     <t>Microbiology6305.dateReportCompleted</t>
   </si>
   <si>
     <t>DATE REPORT COMPLETED (-.03)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.verifyPerson</t>
-  </si>
-  <si>
-    <t>VERIFY PERSON (-.04)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.accessioningInstitution</t>
-  </si>
-  <si>
-    <t>ACCESSIONING INSTITUTION (-.112)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.commentOnSpecimen</t>
-  </si>
-  <si>
-    <t>COMMENT ON SPECIMEN (-.99)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.organism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organism633)
-</t>
-  </si>
-  <si>
-    <t>ORGANISM (-12)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.microbiologyAccession</t>
-  </si>
-  <si>
-    <t>MICROBIOLOGY ACCESSION (-.06)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.ien</t>
-  </si>
-  <si>
-    <t>IEN (-.001)</t>
   </si>
   <si>
     <t>Microbiology6305.collectionSample</t>
@@ -326,116 +304,44 @@
     <t>COLLECTION SAMPLE (-.055)</t>
   </si>
   <si>
-    <t>Microbiology6305.bactRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/BactRptRemark6333)
-</t>
-  </si>
-  <si>
-    <t>BACT RPT REMARK (-13)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.urineScreen</t>
-  </si>
-  <si>
-    <t>URINE SCREEN (-11.57)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.sputumScreen</t>
-  </si>
-  <si>
-    <t>SPUTUM SCREEN (-11.58)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.gramStain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/GramStain6329)
-</t>
-  </si>
-  <si>
-    <t>GRAM STAIN (-11.6)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
-</t>
-  </si>
-  <si>
-    <t>PARASITE RPT REMARK (-17)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptStatus</t>
+    <t>Microbiology6305.tbRptStatus</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
 </t>
   </si>
   <si>
+    <t>TB RPT STATUS (-23)</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus-vista</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycologyRptStatus</t>
+  </si>
+  <si>
+    <t>MYCOLOGY RPT STATUS (-19)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasiteRptStatus</t>
+  </si>
+  <si>
     <t>PARASITE RPT STATUS (-15)</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus-vista</t>
-  </si>
-  <si>
-    <t>Microbiology6305.mycologyRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/MycologyRptRemark6338)
-</t>
-  </si>
-  <si>
-    <t>MYCOLOGY RPT REMARK (-21)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.mycologyRptStatus</t>
-  </si>
-  <si>
-    <t>MYCOLOGY RPT STATUS (-19)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.tbRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/TbRptRemark6341)
-</t>
-  </si>
-  <si>
-    <t>TB RPT REMARK (-27)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.tbRptStatus</t>
-  </si>
-  <si>
-    <t>TB RPT STATUS (-23)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.acidFastStain</t>
-  </si>
-  <si>
-    <t>ACID FAST STAIN (-24)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.virologyRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VirologyRptRemark6344)
-</t>
-  </si>
-  <si>
-    <t>VIROLOGY RPT REMARK (-37)</t>
-  </si>
-  <si>
     <t>Microbiology6305.virologyReportStatus</t>
   </si>
   <si>
     <t>VIROLOGY REPORT STATUS (-34)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.bactRptStatus</t>
+  </si>
+  <si>
+    <t>BACT RPT STATUS (-11.5)</t>
   </si>
 </sst>
 </file>
@@ -737,7 +643,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ25"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.859375" customWidth="true" bestFit="true"/>
@@ -750,7 +656,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="69.6015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="64.25390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1115,13 +1021,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="L4" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="M4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1189,10 +1095,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1215,13 +1121,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1272,7 +1178,7 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1289,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1315,13 +1221,13 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1372,7 +1278,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1389,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1415,7 +1321,7 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>89</v>
@@ -1472,7 +1378,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1515,7 +1421,7 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L8" t="s" s="2">
         <v>91</v>
@@ -1715,13 +1621,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1748,13 +1654,11 @@
         <v>72</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="Y10" s="2"/>
       <c r="Z10" t="s" s="2">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>72</v>
@@ -1789,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1815,13 +1719,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1848,13 +1752,11 @@
         <v>72</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="Y11" s="2"/>
       <c r="Z11" t="s" s="2">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>72</v>
@@ -1872,7 +1774,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1889,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1915,13 +1817,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1948,13 +1850,11 @@
         <v>72</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>72</v>
@@ -1972,7 +1872,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1989,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2015,13 +1915,13 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2048,13 +1948,11 @@
         <v>72</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>72</v>
@@ -2072,7 +1970,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -2089,10 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2115,13 +2013,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2148,13 +2046,11 @@
         <v>72</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>72</v>
@@ -2172,7 +2068,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
@@ -2184,1098 +2080,6 @@
         <v>72</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q17" s="2"/>
-      <c r="R17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K18" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q18" s="2"/>
-      <c r="R18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y18" s="2"/>
-      <c r="Z18" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K19" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q19" s="2"/>
-      <c r="R19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K20" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q20" s="2"/>
-      <c r="R20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y20" s="2"/>
-      <c r="Z20" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K21" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q21" s="2"/>
-      <c r="R21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K22" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q22" s="2"/>
-      <c r="R22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y22" s="2"/>
-      <c r="Z22" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q23" s="2"/>
-      <c r="R23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K24" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q24" s="2"/>
-      <c r="R24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K25" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q25" s="2"/>
-      <c r="R25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y25" s="2"/>
-      <c r="Z25" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="136">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,10 +247,20 @@
     <t>Base</t>
   </si>
   <si>
+    <t>Microbiology6305.orderedTest</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/OrderedTest635)
+</t>
+  </si>
+  <si>
+    <t>ORDERED TEST (-.35)</t>
+  </si>
+  <si>
     <t>Microbiology6305.datetimeSpecimenTaken</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">Element
@@ -260,6 +270,24 @@
     <t>DATE/TIME SPECIMEN TAKEN (-.01)</t>
   </si>
   <si>
+    <t>Microbiology6305.dateReportCompleted</t>
+  </si>
+  <si>
+    <t>DATE REPORT COMPLETED (-.03)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.verifyPerson</t>
+  </si>
+  <si>
+    <t>VERIFY PERSON (-.04)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.accessioningInstitution</t>
+  </si>
+  <si>
+    <t>ACCESSIONING INSTITUTION (-.112)</t>
+  </si>
+  <si>
     <t>Microbiology6305.commentOnSpecimen</t>
   </si>
   <si>
@@ -276,22 +304,6 @@
   </si>
   <si>
     <t>IEN (-.001)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.orderedTest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/OrderedTest635)
-</t>
-  </si>
-  <si>
-    <t>ORDERED TEST (-.35)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.dateReportCompleted</t>
-  </si>
-  <si>
-    <t>DATE REPORT COMPLETED (-.03)</t>
   </si>
   <si>
     <t>Microbiology6305.collectionSample</t>
@@ -304,20 +316,77 @@
     <t>COLLECTION SAMPLE (-.055)</t>
   </si>
   <si>
-    <t>Microbiology6305.tbRptStatus</t>
+    <t>Microbiology6305.organism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organism633)
+</t>
+  </si>
+  <si>
+    <t>ORGANISM (-12)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.bactRptStatus</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
 </t>
   </si>
   <si>
+    <t>BACT RPT STATUS (-11.5)</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus-vista</t>
+  </si>
+  <si>
+    <t>Microbiology6305.urineScreen</t>
+  </si>
+  <si>
+    <t>URINE SCREEN (-11.57)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFMicrobiologyUrineScreenResult-vista</t>
+  </si>
+  <si>
+    <t>Microbiology6305.sputumScreen</t>
+  </si>
+  <si>
+    <t>SPUTUM SCREEN (-11.58)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.gramStain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/GramStain6329)
+</t>
+  </si>
+  <si>
+    <t>GRAM STAIN (-11.6)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.tbRptStatus</t>
+  </si>
+  <si>
     <t>TB RPT STATUS (-23)</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus-vista</t>
+    <t>Microbiology6305.mycobacterium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Mycobacterium6337)
+</t>
+  </si>
+  <si>
+    <t>MYCOBACTERIUM (-26)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.acidFastStain</t>
+  </si>
+  <si>
+    <t>ACID FAST STAIN (-24)</t>
   </si>
   <si>
     <t>Microbiology6305.mycologyRptStatus</t>
@@ -326,22 +395,42 @@
     <t>MYCOLOGY RPT STATUS (-19)</t>
   </si>
   <si>
+    <t>Microbiology6305.fungusyeast</t>
+  </si>
+  <si>
+    <t>FUNGUS/YEAST (-20)</t>
+  </si>
+  <si>
     <t>Microbiology6305.parasiteRptStatus</t>
   </si>
   <si>
     <t>PARASITE RPT STATUS (-15)</t>
   </si>
   <si>
+    <t>Microbiology6305.parasite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Parasite6334)
+</t>
+  </si>
+  <si>
+    <t>PARASITE (-16)</t>
+  </si>
+  <si>
     <t>Microbiology6305.virologyReportStatus</t>
   </si>
   <si>
     <t>VIROLOGY REPORT STATUS (-34)</t>
   </si>
   <si>
-    <t>Microbiology6305.bactRptStatus</t>
-  </si>
-  <si>
-    <t>BACT RPT STATUS (-11.5)</t>
+    <t>Microbiology6305.virus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Virus6343)
+</t>
+  </si>
+  <si>
+    <t>VIRUS (-36)</t>
   </si>
 </sst>
 </file>
@@ -643,7 +732,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AJ25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.859375" customWidth="true" bestFit="true"/>
@@ -656,7 +745,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="64.25390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="64.79296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -671,7 +760,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.02734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.34765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -1021,13 +1110,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1095,10 +1184,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1121,13 +1210,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1178,7 +1267,7 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1195,10 +1284,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1221,13 +1310,13 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1278,7 +1367,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1295,10 +1384,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1321,7 +1410,7 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>89</v>
@@ -1378,7 +1467,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1421,7 +1510,7 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L8" t="s" s="2">
         <v>91</v>
@@ -1521,13 +1610,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="M9" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1595,10 +1684,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1621,13 +1710,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1654,11 +1743,13 @@
         <v>72</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="Y10" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z10" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>72</v>
@@ -1676,7 +1767,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1693,10 +1784,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1719,13 +1810,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1752,11 +1843,13 @@
         <v>72</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="Y11" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z11" t="s" s="2">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>72</v>
@@ -1774,7 +1867,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1791,10 +1884,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1817,13 +1910,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1850,29 +1943,31 @@
         <v>72</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="Y12" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1889,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1915,13 +2010,13 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1948,11 +2043,11 @@
         <v>72</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>72</v>
@@ -1970,7 +2065,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -1987,10 +2082,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2013,13 +2108,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2046,11 +2141,11 @@
         <v>72</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>72</v>
@@ -2068,18 +2163,1110 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="Y17" s="2"/>
+      <c r="Z17" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AG14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="Y20" s="2"/>
+      <c r="Z20" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="Y22" s="2"/>
+      <c r="Z22" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="Y24" s="2"/>
+      <c r="Z24" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="151">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -316,6 +316,16 @@
     <t>COLLECTION SAMPLE (-.055)</t>
   </si>
   <si>
+    <t>Microbiology6305.bactRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/BactRptRemark6333)
+</t>
+  </si>
+  <si>
+    <t>BACT RPT REMARK (-13)</t>
+  </si>
+  <si>
     <t>Microbiology6305.organism</t>
   </si>
   <si>
@@ -367,38 +377,14 @@
     <t>GRAM STAIN (-11.6)</t>
   </si>
   <si>
-    <t>Microbiology6305.tbRptStatus</t>
-  </si>
-  <si>
-    <t>TB RPT STATUS (-23)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.mycobacterium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Mycobacterium6337)
+    <t>Microbiology6305.parasiteRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
 </t>
   </si>
   <si>
-    <t>MYCOBACTERIUM (-26)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.acidFastStain</t>
-  </si>
-  <si>
-    <t>ACID FAST STAIN (-24)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.mycologyRptStatus</t>
-  </si>
-  <si>
-    <t>MYCOLOGY RPT STATUS (-19)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.fungusyeast</t>
-  </si>
-  <si>
-    <t>FUNGUS/YEAST (-20)</t>
+    <t>PARASITE RPT REMARK (-17)</t>
   </si>
   <si>
     <t>Microbiology6305.parasiteRptStatus</t>
@@ -415,6 +401,70 @@
   </si>
   <si>
     <t>PARASITE (-16)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycologyRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/MycologyRptRemark6338)
+</t>
+  </si>
+  <si>
+    <t>MYCOLOGY RPT REMARK (-21)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycologyRptStatus</t>
+  </si>
+  <si>
+    <t>MYCOLOGY RPT STATUS (-19)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.fungusyeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Fungusyeast6337)
+</t>
+  </si>
+  <si>
+    <t>FUNGUS/YEAST (-20)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.tbRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/TbRptRemark6341)
+</t>
+  </si>
+  <si>
+    <t>TB RPT REMARK (-27)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.tbRptStatus</t>
+  </si>
+  <si>
+    <t>TB RPT STATUS (-23)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycobacterium</t>
+  </si>
+  <si>
+    <t>MYCOBACTERIUM (-26)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.acidFastStain</t>
+  </si>
+  <si>
+    <t>ACID FAST STAIN (-24)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.virologyRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VirologyRptRemark6344)
+</t>
+  </si>
+  <si>
+    <t>VIROLOGY RPT REMARK (-37)</t>
   </si>
   <si>
     <t>Microbiology6305.virologyReportStatus</t>
@@ -732,7 +782,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ25"/>
+  <dimension ref="A1:AJ30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.859375" customWidth="true" bestFit="true"/>
@@ -745,7 +795,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="64.79296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.6015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2043,11 +2093,13 @@
         <v>72</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>72</v>
@@ -2082,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2108,13 +2160,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2141,7 +2193,7 @@
         <v>72</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
@@ -2163,7 +2215,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
@@ -2206,7 +2258,7 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>111</v>
@@ -2239,13 +2291,11 @@
         <v>72</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>72</v>
@@ -2280,10 +2330,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2306,7 +2356,7 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>114</v>
@@ -2363,7 +2413,7 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
@@ -2406,13 +2456,13 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2439,11 +2489,13 @@
         <v>72</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>72</v>
@@ -2478,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2504,13 +2556,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2561,7 +2613,7 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
@@ -2578,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2604,13 +2656,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2637,13 +2689,11 @@
         <v>72</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>72</v>
@@ -2661,7 +2711,7 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
@@ -2678,10 +2728,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2704,13 +2754,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2737,11 +2787,13 @@
         <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>72</v>
@@ -2759,7 +2811,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -2776,10 +2828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2802,13 +2854,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2859,7 +2911,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -2876,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2902,13 +2954,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2935,11 +2987,11 @@
         <v>72</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>72</v>
@@ -2957,7 +3009,7 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -2974,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3000,13 +3052,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3057,7 +3109,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3074,10 +3126,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3100,13 +3152,13 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3133,11 +3185,13 @@
         <v>72</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>72</v>
@@ -3155,7 +3209,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3172,10 +3226,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3198,13 +3252,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3231,13 +3285,11 @@
         <v>72</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>72</v>
@@ -3255,7 +3307,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3267,6 +3319,504 @@
         <v>72</v>
       </c>
       <c r="AJ25" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="Y29" s="2"/>
+      <c r="Z29" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -387,12 +387,6 @@
     <t>PARASITE RPT REMARK (-17)</t>
   </si>
   <si>
-    <t>Microbiology6305.parasiteRptStatus</t>
-  </si>
-  <si>
-    <t>PARASITE RPT STATUS (-15)</t>
-  </si>
-  <si>
     <t>Microbiology6305.parasite</t>
   </si>
   <si>
@@ -403,6 +397,12 @@
     <t>PARASITE (-16)</t>
   </si>
   <si>
+    <t>Microbiology6305.parasiteRptStatus</t>
+  </si>
+  <si>
+    <t>PARASITE RPT STATUS (-15)</t>
+  </si>
+  <si>
     <t>Microbiology6305.mycologyRptRemark</t>
   </si>
   <si>
@@ -413,12 +413,6 @@
     <t>MYCOLOGY RPT REMARK (-21)</t>
   </si>
   <si>
-    <t>Microbiology6305.mycologyRptStatus</t>
-  </si>
-  <si>
-    <t>MYCOLOGY RPT STATUS (-19)</t>
-  </si>
-  <si>
     <t>Microbiology6305.fungusyeast</t>
   </si>
   <si>
@@ -429,6 +423,12 @@
     <t>FUNGUS/YEAST (-20)</t>
   </si>
   <si>
+    <t>Microbiology6305.mycologyRptStatus</t>
+  </si>
+  <si>
+    <t>MYCOLOGY RPT STATUS (-19)</t>
+  </si>
+  <si>
     <t>Microbiology6305.tbRptRemark</t>
   </si>
   <si>
@@ -439,16 +439,16 @@
     <t>TB RPT REMARK (-27)</t>
   </si>
   <si>
+    <t>Microbiology6305.mycobacterium</t>
+  </si>
+  <si>
+    <t>MYCOBACTERIUM (-26)</t>
+  </si>
+  <si>
     <t>Microbiology6305.tbRptStatus</t>
   </si>
   <si>
     <t>TB RPT STATUS (-23)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.mycobacterium</t>
-  </si>
-  <si>
-    <t>MYCOBACTERIUM (-26)</t>
   </si>
   <si>
     <t>Microbiology6305.acidFastStain</t>
@@ -467,12 +467,6 @@
     <t>VIROLOGY RPT REMARK (-37)</t>
   </si>
   <si>
-    <t>Microbiology6305.virologyReportStatus</t>
-  </si>
-  <si>
-    <t>VIROLOGY REPORT STATUS (-34)</t>
-  </si>
-  <si>
     <t>Microbiology6305.virus</t>
   </si>
   <si>
@@ -481,6 +475,12 @@
   </si>
   <si>
     <t>VIRUS (-36)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.virologyReportStatus</t>
+  </si>
+  <si>
+    <t>VIROLOGY REPORT STATUS (-34)</t>
   </si>
 </sst>
 </file>
@@ -2656,13 +2656,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2689,11 +2689,13 @@
         <v>72</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>72</v>
@@ -2728,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2754,7 +2756,7 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>125</v>
@@ -2787,13 +2789,11 @@
         <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>72</v>
@@ -2811,7 +2811,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -2954,13 +2954,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2987,11 +2987,13 @@
         <v>72</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>72</v>
@@ -3026,10 +3028,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3052,7 +3054,7 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>133</v>
@@ -3085,13 +3087,11 @@
         <v>72</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>72</v>
@@ -3109,7 +3109,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3252,7 +3252,7 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>138</v>
@@ -3285,11 +3285,13 @@
         <v>72</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>72</v>
@@ -3350,7 +3352,7 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>140</v>
@@ -3383,13 +3385,11 @@
         <v>72</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>72</v>
@@ -3650,13 +3650,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3683,11 +3683,13 @@
         <v>72</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>72</v>
@@ -3722,10 +3724,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3748,7 +3750,7 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>150</v>
@@ -3781,13 +3783,11 @@
         <v>72</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>72</v>
@@ -3805,7 +3805,7 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="152">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,10 +247,20 @@
     <t>Base</t>
   </si>
   <si>
+    <t>Microbiology6305.virus</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Virus6343)
+</t>
+  </si>
+  <si>
+    <t>VIRUS (-36)</t>
+  </si>
+  <si>
     <t>Microbiology6305.orderedTest</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/OrderedTest635)
@@ -260,6 +270,16 @@
     <t>ORDERED TEST (-.35)</t>
   </si>
   <si>
+    <t>Microbiology6305.virologyRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VirologyRptRemark6344)
+</t>
+  </si>
+  <si>
+    <t>VIROLOGY RPT REMARK (-37)</t>
+  </si>
+  <si>
     <t>Microbiology6305.datetimeSpecimenTaken</t>
   </si>
   <si>
@@ -288,6 +308,22 @@
     <t>ACCESSIONING INSTITUTION (-.112)</t>
   </si>
   <si>
+    <t>Microbiology6305.virologyReportStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>VIROLOGY REPORT STATUS (-34)</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus-vista</t>
+  </si>
+  <si>
     <t>Microbiology6305.commentOnSpecimen</t>
   </si>
   <si>
@@ -316,6 +352,90 @@
     <t>COLLECTION SAMPLE (-.055)</t>
   </si>
   <si>
+    <t>Microbiology6305.mycobacterium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Mycobacterium6339)
+</t>
+  </si>
+  <si>
+    <t>MYCOBACTERIUM (-26)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.tbRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/TbRptRemark6341)
+</t>
+  </si>
+  <si>
+    <t>TB RPT REMARK (-27)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.tbRptStatus</t>
+  </si>
+  <si>
+    <t>TB RPT STATUS (-23)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.acidFastStain</t>
+  </si>
+  <si>
+    <t>ACID FAST STAIN (-24)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.fungusyeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Fungusyeast6337)
+</t>
+  </si>
+  <si>
+    <t>FUNGUS/YEAST (-20)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycologyRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/MycologyRptRemark6338)
+</t>
+  </si>
+  <si>
+    <t>MYCOLOGY RPT REMARK (-21)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycologyRptStatus</t>
+  </si>
+  <si>
+    <t>MYCOLOGY RPT STATUS (-19)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Parasite6334)
+</t>
+  </si>
+  <si>
+    <t>PARASITE (-16)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasiteRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
+</t>
+  </si>
+  <si>
+    <t>PARASITE RPT REMARK (-17)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasiteRptStatus</t>
+  </si>
+  <si>
+    <t>PARASITE RPT STATUS (-15)</t>
+  </si>
+  <si>
     <t>Microbiology6305.bactRptRemark</t>
   </si>
   <si>
@@ -339,17 +459,7 @@
     <t>Microbiology6305.bactRptStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
     <t>BACT RPT STATUS (-11.5)</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus-vista</t>
   </si>
   <si>
     <t>Microbiology6305.urineScreen</t>
@@ -375,112 +485,6 @@
   </si>
   <si>
     <t>GRAM STAIN (-11.6)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
-</t>
-  </si>
-  <si>
-    <t>PARASITE RPT REMARK (-17)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Parasite6334)
-</t>
-  </si>
-  <si>
-    <t>PARASITE (-16)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptStatus</t>
-  </si>
-  <si>
-    <t>PARASITE RPT STATUS (-15)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.mycologyRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/MycologyRptRemark6338)
-</t>
-  </si>
-  <si>
-    <t>MYCOLOGY RPT REMARK (-21)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.fungusyeast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Fungusyeast6337)
-</t>
-  </si>
-  <si>
-    <t>FUNGUS/YEAST (-20)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.mycologyRptStatus</t>
-  </si>
-  <si>
-    <t>MYCOLOGY RPT STATUS (-19)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.tbRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/TbRptRemark6341)
-</t>
-  </si>
-  <si>
-    <t>TB RPT REMARK (-27)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.mycobacterium</t>
-  </si>
-  <si>
-    <t>MYCOBACTERIUM (-26)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.tbRptStatus</t>
-  </si>
-  <si>
-    <t>TB RPT STATUS (-23)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.acidFastStain</t>
-  </si>
-  <si>
-    <t>ACID FAST STAIN (-24)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.virologyRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VirologyRptRemark6344)
-</t>
-  </si>
-  <si>
-    <t>VIROLOGY RPT REMARK (-37)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.virus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Virus6343)
-</t>
-  </si>
-  <si>
-    <t>VIRUS (-36)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.virologyReportStatus</t>
-  </si>
-  <si>
-    <t>VIROLOGY REPORT STATUS (-34)</t>
   </si>
 </sst>
 </file>
@@ -1260,13 +1264,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1334,10 +1338,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1360,13 +1364,13 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1417,7 +1421,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1434,10 +1438,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1460,13 +1464,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1517,7 +1521,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1534,10 +1538,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1560,13 +1564,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1617,7 +1621,7 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1634,10 +1638,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1660,13 +1664,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1717,7 +1721,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1734,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1760,13 +1764,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1793,13 +1797,11 @@
         <v>72</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="Y10" s="2"/>
       <c r="Z10" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>72</v>
@@ -1817,7 +1819,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1834,10 +1836,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1860,13 +1862,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1917,7 +1919,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1934,10 +1936,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1960,13 +1962,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2017,7 +2019,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -2034,10 +2036,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2060,13 +2062,13 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2117,7 +2119,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -2134,10 +2136,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2160,13 +2162,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2193,11 +2195,13 @@
         <v>72</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>72</v>
@@ -2215,7 +2219,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
@@ -2258,13 +2262,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2291,11 +2295,13 @@
         <v>72</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>72</v>
@@ -2356,13 +2362,13 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2430,10 +2436,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2456,7 +2462,7 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>117</v>
@@ -2489,13 +2495,11 @@
         <v>72</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>72</v>
@@ -2513,7 +2517,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2556,13 +2560,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="M18" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2630,10 +2634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2656,13 +2660,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>123</v>
-      </c>
       <c r="M19" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2713,7 +2717,7 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
@@ -2730,10 +2734,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2756,7 +2760,7 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>125</v>
@@ -2789,11 +2793,13 @@
         <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>72</v>
@@ -2811,7 +2817,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -2854,13 +2860,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>128</v>
-      </c>
       <c r="M21" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2887,13 +2893,11 @@
         <v>72</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>72</v>
@@ -2928,10 +2932,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2954,13 +2958,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>131</v>
-      </c>
       <c r="M22" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3011,7 +3015,7 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -3028,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3054,7 +3058,7 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>133</v>
@@ -3087,11 +3091,13 @@
         <v>72</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>72</v>
@@ -3109,7 +3115,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3152,13 +3158,13 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>136</v>
-      </c>
       <c r="M24" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3185,13 +3191,11 @@
         <v>72</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>72</v>
@@ -3226,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3252,7 +3256,7 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>138</v>
@@ -3309,7 +3313,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3352,13 +3356,13 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3385,11 +3389,13 @@
         <v>72</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>72</v>
@@ -3424,10 +3430,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3450,13 +3456,13 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3483,13 +3489,11 @@
         <v>72</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>72</v>
@@ -3507,7 +3511,7 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>73</v>
@@ -3524,10 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3550,7 +3554,7 @@
         <v>72</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>145</v>
@@ -3583,13 +3587,11 @@
         <v>72</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>72</v>
@@ -3607,7 +3609,7 @@
         <v>72</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>73</v>
@@ -3624,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3650,7 +3652,7 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>148</v>
@@ -3707,7 +3709,7 @@
         <v>72</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>73</v>
@@ -3750,13 +3752,13 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3783,11 +3785,13 @@
         <v>72</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>72</v>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,6 +352,32 @@
     <t>COLLECTION SAMPLE (-.055)</t>
   </si>
   <si>
+    <t>Microbiology6305.parasite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Parasite6334)
+</t>
+  </si>
+  <si>
+    <t>PARASITE (-16)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasiteRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
+</t>
+  </si>
+  <si>
+    <t>PARASITE RPT REMARK (-17)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasiteRptStatus</t>
+  </si>
+  <si>
+    <t>PARASITE RPT STATUS (-15)</t>
+  </si>
+  <si>
     <t>Microbiology6305.mycobacterium</t>
   </si>
   <si>
@@ -408,32 +434,6 @@
   </si>
   <si>
     <t>MYCOLOGY RPT STATUS (-19)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Parasite6334)
-</t>
-  </si>
-  <si>
-    <t>PARASITE (-16)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
-</t>
-  </si>
-  <si>
-    <t>PARASITE RPT REMARK (-17)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptStatus</t>
-  </si>
-  <si>
-    <t>PARASITE RPT STATUS (-15)</t>
   </si>
   <si>
     <t>Microbiology6305.bactRptRemark</t>
@@ -2560,13 +2560,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2660,13 +2660,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2717,7 +2717,7 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2760,7 +2760,7 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>125</v>
@@ -2793,13 +2793,11 @@
         <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>72</v>
@@ -2817,7 +2815,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -2860,7 +2858,7 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>127</v>
@@ -2893,11 +2891,13 @@
         <v>72</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>72</v>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file MICROBIOLOGY (63.05)</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the source MICROBIOLOGY (63.05)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,10 +247,237 @@
     <t>Base</t>
   </si>
   <si>
+    <t>Microbiology6305.orderedTest</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/OrderedTest635)
+</t>
+  </si>
+  <si>
+    <t>ORDERED TEST (-.35)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.datetimeSpecimenTaken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Element
+</t>
+  </si>
+  <si>
+    <t>DATE/TIME SPECIMEN TAKEN (-.01)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.dateReportCompleted</t>
+  </si>
+  <si>
+    <t>DATE REPORT COMPLETED (-.03)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.verifyPerson</t>
+  </si>
+  <si>
+    <t>VERIFY PERSON (-.04)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.accessioningInstitution</t>
+  </si>
+  <si>
+    <t>ACCESSIONING INSTITUTION (-.112)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.commentOnSpecimen</t>
+  </si>
+  <si>
+    <t>COMMENT ON SPECIMEN (-.99)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.ien</t>
+  </si>
+  <si>
+    <t>IEN (-.001)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.microbiologyAccession</t>
+  </si>
+  <si>
+    <t>MICROBIOLOGY ACCESSION (-.06)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.collectionSample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/CollectionSample62)
+</t>
+  </si>
+  <si>
+    <t>COLLECTION SAMPLE (-.055)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.bactRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/BactRptRemark6333)
+</t>
+  </si>
+  <si>
+    <t>BACT RPT REMARK (-13)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.organism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organism633)
+</t>
+  </si>
+  <si>
+    <t>ORGANISM (-12)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.bactRptStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>BACT RPT STATUS (-11.5)</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus-vista</t>
+  </si>
+  <si>
+    <t>Microbiology6305.urineScreen</t>
+  </si>
+  <si>
+    <t>URINE SCREEN (-11.57)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFMicrobiologyUrineScreenResult-vista</t>
+  </si>
+  <si>
+    <t>Microbiology6305.sputumScreen</t>
+  </si>
+  <si>
+    <t>SPUTUM SCREEN (-11.58)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.gramStain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/GramStain6329)
+</t>
+  </si>
+  <si>
+    <t>GRAM STAIN (-11.6)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.tbRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/TbRptRemark6341)
+</t>
+  </si>
+  <si>
+    <t>TB RPT REMARK (-27)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.tbRptStatus</t>
+  </si>
+  <si>
+    <t>TB RPT STATUS (-23)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.acidFastStain</t>
+  </si>
+  <si>
+    <t>ACID FAST STAIN (-24)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycobacterium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Mycobacterium6339)
+</t>
+  </si>
+  <si>
+    <t>MYCOBACTERIUM (-26)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycologyRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/MycologyRptRemark6338)
+</t>
+  </si>
+  <si>
+    <t>MYCOLOGY RPT REMARK (-21)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycologyRptStatus</t>
+  </si>
+  <si>
+    <t>MYCOLOGY RPT STATUS (-19)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.fungusyeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Fungusyeast6337)
+</t>
+  </si>
+  <si>
+    <t>FUNGUS/YEAST (-20)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasiteRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
+</t>
+  </si>
+  <si>
+    <t>PARASITE RPT REMARK (-17)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasiteRptStatus</t>
+  </si>
+  <si>
+    <t>PARASITE RPT STATUS (-15)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Parasite6334)
+</t>
+  </si>
+  <si>
+    <t>PARASITE (-16)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.virologyRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VirologyRptRemark6344)
+</t>
+  </si>
+  <si>
+    <t>VIROLOGY RPT REMARK (-37)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.virologyReportStatus</t>
+  </si>
+  <si>
+    <t>VIROLOGY REPORT STATUS (-34)</t>
+  </si>
+  <si>
     <t>Microbiology6305.virus</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Virus6343)
@@ -258,233 +485,6 @@
   </si>
   <si>
     <t>VIRUS (-36)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.orderedTest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/OrderedTest635)
-</t>
-  </si>
-  <si>
-    <t>ORDERED TEST (-.35)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.virologyRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VirologyRptRemark6344)
-</t>
-  </si>
-  <si>
-    <t>VIROLOGY RPT REMARK (-37)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.datetimeSpecimenTaken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Element
-</t>
-  </si>
-  <si>
-    <t>DATE/TIME SPECIMEN TAKEN (-.01)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.dateReportCompleted</t>
-  </si>
-  <si>
-    <t>DATE REPORT COMPLETED (-.03)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.verifyPerson</t>
-  </si>
-  <si>
-    <t>VERIFY PERSON (-.04)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.accessioningInstitution</t>
-  </si>
-  <si>
-    <t>ACCESSIONING INSTITUTION (-.112)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.virologyReportStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>VIROLOGY REPORT STATUS (-34)</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus-vista</t>
-  </si>
-  <si>
-    <t>Microbiology6305.commentOnSpecimen</t>
-  </si>
-  <si>
-    <t>COMMENT ON SPECIMEN (-.99)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.microbiologyAccession</t>
-  </si>
-  <si>
-    <t>MICROBIOLOGY ACCESSION (-.06)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.ien</t>
-  </si>
-  <si>
-    <t>IEN (-.001)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.collectionSample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/CollectionSample62)
-</t>
-  </si>
-  <si>
-    <t>COLLECTION SAMPLE (-.055)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Parasite6334)
-</t>
-  </si>
-  <si>
-    <t>PARASITE (-16)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
-</t>
-  </si>
-  <si>
-    <t>PARASITE RPT REMARK (-17)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptStatus</t>
-  </si>
-  <si>
-    <t>PARASITE RPT STATUS (-15)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.mycobacterium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Mycobacterium6339)
-</t>
-  </si>
-  <si>
-    <t>MYCOBACTERIUM (-26)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.tbRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/TbRptRemark6341)
-</t>
-  </si>
-  <si>
-    <t>TB RPT REMARK (-27)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.tbRptStatus</t>
-  </si>
-  <si>
-    <t>TB RPT STATUS (-23)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.acidFastStain</t>
-  </si>
-  <si>
-    <t>ACID FAST STAIN (-24)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.fungusyeast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Fungusyeast6337)
-</t>
-  </si>
-  <si>
-    <t>FUNGUS/YEAST (-20)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.mycologyRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/MycologyRptRemark6338)
-</t>
-  </si>
-  <si>
-    <t>MYCOLOGY RPT REMARK (-21)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.mycologyRptStatus</t>
-  </si>
-  <si>
-    <t>MYCOLOGY RPT STATUS (-19)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.bactRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/BactRptRemark6333)
-</t>
-  </si>
-  <si>
-    <t>BACT RPT REMARK (-13)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.organism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organism633)
-</t>
-  </si>
-  <si>
-    <t>ORGANISM (-12)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.bactRptStatus</t>
-  </si>
-  <si>
-    <t>BACT RPT STATUS (-11.5)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.urineScreen</t>
-  </si>
-  <si>
-    <t>URINE SCREEN (-11.57)</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFMicrobiologyUrineScreenResult-vista</t>
-  </si>
-  <si>
-    <t>Microbiology6305.sputumScreen</t>
-  </si>
-  <si>
-    <t>SPUTUM SCREEN (-11.58)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.gramStain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/GramStain6329)
-</t>
-  </si>
-  <si>
-    <t>GRAM STAIN (-11.6)</t>
   </si>
 </sst>
 </file>
@@ -1264,13 +1264,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="M5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1364,13 +1364,13 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1421,7 +1421,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1464,13 +1464,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1521,7 +1521,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1564,13 +1564,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1621,7 +1621,7 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1664,13 +1664,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1721,7 +1721,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1764,13 +1764,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1797,11 +1797,13 @@
         <v>72</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="Y10" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z10" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>72</v>
@@ -1819,7 +1821,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1836,10 +1838,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1862,13 +1864,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1919,7 +1921,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1936,10 +1938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1962,13 +1964,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2019,7 +2021,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -2036,10 +2038,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2062,13 +2064,13 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2119,7 +2121,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -2136,10 +2138,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2162,13 +2164,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2195,13 +2197,11 @@
         <v>72</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>72</v>
@@ -2219,7 +2219,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
@@ -2262,13 +2262,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="M15" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2295,13 +2295,11 @@
         <v>72</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>72</v>
@@ -2362,13 +2360,13 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M16" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2436,10 +2434,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2462,7 +2460,7 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>117</v>
@@ -2495,11 +2493,13 @@
         <v>72</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>72</v>
@@ -2517,7 +2517,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2660,13 +2660,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>123</v>
-      </c>
       <c r="M19" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2693,13 +2693,11 @@
         <v>72</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>72</v>
@@ -2734,10 +2732,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2760,13 +2758,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2793,11 +2791,13 @@
         <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>72</v>
@@ -2815,7 +2815,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2858,7 +2858,7 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>127</v>
@@ -2915,7 +2915,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -3058,13 +3058,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>133</v>
-      </c>
       <c r="M23" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3091,13 +3091,11 @@
         <v>72</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>72</v>
@@ -3132,10 +3130,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3158,7 +3156,7 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>135</v>
@@ -3191,11 +3189,13 @@
         <v>72</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>72</v>
@@ -3213,7 +3213,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3356,13 +3356,13 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>141</v>
-      </c>
       <c r="M26" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3389,13 +3389,11 @@
         <v>72</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>72</v>
@@ -3430,10 +3428,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3456,7 +3454,7 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>143</v>
@@ -3489,11 +3487,13 @@
         <v>72</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>72</v>
@@ -3511,7 +3511,7 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>73</v>
@@ -3554,13 +3554,13 @@
         <v>72</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3587,11 +3587,13 @@
         <v>72</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>72</v>
@@ -3652,7 +3654,7 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>148</v>
@@ -3685,13 +3687,11 @@
         <v>72</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>72</v>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -294,16 +294,16 @@
     <t>COMMENT ON SPECIMEN (-.99)</t>
   </si>
   <si>
+    <t>Microbiology6305.microbiologyAccession</t>
+  </si>
+  <si>
+    <t>MICROBIOLOGY ACCESSION (-.06)</t>
+  </si>
+  <si>
     <t>Microbiology6305.ien</t>
   </si>
   <si>
     <t>IEN (-.001)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.microbiologyAccession</t>
-  </si>
-  <si>
-    <t>MICROBIOLOGY ACCESSION (-.06)</t>
   </si>
   <si>
     <t>Microbiology6305.collectionSample</t>
@@ -377,6 +377,58 @@
     <t>GRAM STAIN (-11.6)</t>
   </si>
   <si>
+    <t>Microbiology6305.parasiteRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
+</t>
+  </si>
+  <si>
+    <t>PARASITE RPT REMARK (-17)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Parasite6334)
+</t>
+  </si>
+  <si>
+    <t>PARASITE (-16)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.parasiteRptStatus</t>
+  </si>
+  <si>
+    <t>PARASITE RPT STATUS (-15)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycologyRptRemark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/MycologyRptRemark6338)
+</t>
+  </si>
+  <si>
+    <t>MYCOLOGY RPT REMARK (-21)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.fungusyeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Fungusyeast6337)
+</t>
+  </si>
+  <si>
+    <t>FUNGUS/YEAST (-20)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.mycologyRptStatus</t>
+  </si>
+  <si>
+    <t>MYCOLOGY RPT STATUS (-19)</t>
+  </si>
+  <si>
     <t>Microbiology6305.tbRptRemark</t>
   </si>
   <si>
@@ -387,18 +439,6 @@
     <t>TB RPT REMARK (-27)</t>
   </si>
   <si>
-    <t>Microbiology6305.tbRptStatus</t>
-  </si>
-  <si>
-    <t>TB RPT STATUS (-23)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.acidFastStain</t>
-  </si>
-  <si>
-    <t>ACID FAST STAIN (-24)</t>
-  </si>
-  <si>
     <t>Microbiology6305.mycobacterium</t>
   </si>
   <si>
@@ -409,56 +449,16 @@
     <t>MYCOBACTERIUM (-26)</t>
   </si>
   <si>
-    <t>Microbiology6305.mycologyRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/MycologyRptRemark6338)
-</t>
-  </si>
-  <si>
-    <t>MYCOLOGY RPT REMARK (-21)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.mycologyRptStatus</t>
-  </si>
-  <si>
-    <t>MYCOLOGY RPT STATUS (-19)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.fungusyeast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Fungusyeast6337)
-</t>
-  </si>
-  <si>
-    <t>FUNGUS/YEAST (-20)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptRemark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ParasiteRptRemark6336)
-</t>
-  </si>
-  <si>
-    <t>PARASITE RPT REMARK (-17)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptStatus</t>
-  </si>
-  <si>
-    <t>PARASITE RPT STATUS (-15)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Parasite6334)
-</t>
-  </si>
-  <si>
-    <t>PARASITE (-16)</t>
+    <t>Microbiology6305.tbRptStatus</t>
+  </si>
+  <si>
+    <t>TB RPT STATUS (-23)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.acidFastStain</t>
+  </si>
+  <si>
+    <t>ACID FAST STAIN (-24)</t>
   </si>
   <si>
     <t>Microbiology6305.virologyRptRemark</t>
@@ -471,12 +471,6 @@
     <t>VIROLOGY RPT REMARK (-37)</t>
   </si>
   <si>
-    <t>Microbiology6305.virologyReportStatus</t>
-  </si>
-  <si>
-    <t>VIROLOGY REPORT STATUS (-34)</t>
-  </si>
-  <si>
     <t>Microbiology6305.virus</t>
   </si>
   <si>
@@ -485,6 +479,12 @@
   </si>
   <si>
     <t>VIRUS (-36)</t>
+  </si>
+  <si>
+    <t>Microbiology6305.virologyReportStatus</t>
+  </si>
+  <si>
+    <t>VIROLOGY REPORT STATUS (-34)</t>
   </si>
 </sst>
 </file>
@@ -2660,13 +2660,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2693,11 +2693,13 @@
         <v>72</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>72</v>
@@ -2732,10 +2734,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2758,13 +2760,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2791,13 +2793,11 @@
         <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>72</v>
@@ -2815,7 +2815,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2858,13 +2858,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2915,7 +2915,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -2932,10 +2932,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2958,13 +2958,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3015,7 +3015,7 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3061,10 +3061,10 @@
         <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3113,7 +3113,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3156,13 +3156,13 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3213,7 +3213,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3256,13 +3256,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3313,7 +3313,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3359,10 +3359,10 @@
         <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3411,7 +3411,7 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
@@ -3428,10 +3428,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3454,7 +3454,7 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>143</v>
@@ -3511,7 +3511,7 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>73</v>
@@ -3654,13 +3654,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3687,11 +3687,13 @@
         <v>72</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>72</v>
@@ -3726,10 +3728,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3752,7 +3754,7 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>151</v>
@@ -3785,13 +3787,11 @@
         <v>72</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>72</v>
@@ -3809,7 +3809,7 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -387,6 +387,12 @@
     <t>PARASITE RPT REMARK (-17)</t>
   </si>
   <si>
+    <t>Microbiology6305.parasiteRptStatus</t>
+  </si>
+  <si>
+    <t>PARASITE RPT STATUS (-15)</t>
+  </si>
+  <si>
     <t>Microbiology6305.parasite</t>
   </si>
   <si>
@@ -395,12 +401,6 @@
   </si>
   <si>
     <t>PARASITE (-16)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.parasiteRptStatus</t>
-  </si>
-  <si>
-    <t>PARASITE RPT STATUS (-15)</t>
   </si>
   <si>
     <t>Microbiology6305.mycologyRptRemark</t>
@@ -2660,13 +2660,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>123</v>
-      </c>
       <c r="M19" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2693,13 +2693,11 @@
         <v>72</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>72</v>
@@ -2734,10 +2732,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2760,7 +2758,7 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>125</v>
@@ -2793,11 +2791,13 @@
         <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>72</v>
@@ -2815,7 +2815,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -349,7 +349,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus-vista</t>
+    <t>http://va.gov/fhir/ValueSet/LabObservationStatus-vista</t>
   </si>
   <si>
     <t>Microbiology6305.urineScreen</t>
@@ -358,7 +358,7 @@
     <t>URINE SCREEN (-11.57)</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFMicrobiologyUrineScreenResult-vista</t>
+    <t>http://va.gov/fhir/ValueSet/MicrobiologyUrineScreenResult-vista</t>
   </si>
   <si>
     <t>Microbiology6305.sputumScreen</t>
@@ -814,7 +814,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.34765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -413,6 +413,12 @@
     <t>MYCOLOGY RPT REMARK (-21)</t>
   </si>
   <si>
+    <t>Microbiology6305.mycologyRptStatus</t>
+  </si>
+  <si>
+    <t>MYCOLOGY RPT STATUS (-19)</t>
+  </si>
+  <si>
     <t>Microbiology6305.fungusyeast</t>
   </si>
   <si>
@@ -423,12 +429,6 @@
     <t>FUNGUS/YEAST (-20)</t>
   </si>
   <si>
-    <t>Microbiology6305.mycologyRptStatus</t>
-  </si>
-  <si>
-    <t>MYCOLOGY RPT STATUS (-19)</t>
-  </si>
-  <si>
     <t>Microbiology6305.tbRptRemark</t>
   </si>
   <si>
@@ -471,6 +471,12 @@
     <t>VIROLOGY RPT REMARK (-37)</t>
   </si>
   <si>
+    <t>Microbiology6305.virologyReportStatus</t>
+  </si>
+  <si>
+    <t>VIROLOGY REPORT STATUS (-34)</t>
+  </si>
+  <si>
     <t>Microbiology6305.virus</t>
   </si>
   <si>
@@ -479,12 +485,6 @@
   </si>
   <si>
     <t>VIRUS (-36)</t>
-  </si>
-  <si>
-    <t>Microbiology6305.virologyReportStatus</t>
-  </si>
-  <si>
-    <t>VIROLOGY REPORT STATUS (-34)</t>
   </si>
 </sst>
 </file>
@@ -2958,13 +2958,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>131</v>
-      </c>
       <c r="M22" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2991,13 +2991,11 @@
         <v>72</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>72</v>
@@ -3032,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3058,7 +3056,7 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>133</v>
@@ -3091,11 +3089,13 @@
         <v>72</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>72</v>
@@ -3113,7 +3113,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3654,13 +3654,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>149</v>
-      </c>
       <c r="M29" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3687,13 +3687,11 @@
         <v>72</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>72</v>
@@ -3728,10 +3726,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3754,7 +3752,7 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>151</v>
@@ -3787,11 +3785,13 @@
         <v>72</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>72</v>
@@ -3809,7 +3809,7 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-Microbiology6305.xlsx
+++ b/docs/StructureDefinition-Microbiology6305.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
